--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD9F241-B60E-441D-A17F-8D0CE517DDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91171438-25DC-4C1B-B230-0DEB57F2022F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6240" yWindow="3735" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,78 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Admin</author>
+  </authors>
+  <commentList>
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{31693E38-24A4-47D2-B27B-C8AB67E9FCF7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:
+-2小于</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{C4206D52-59B6-491F-863D-BFDD0CF59D4B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,15 +141,127 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>检查属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检查Buff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ConditionName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParamList</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断谁技能期间是否被打了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckBeDamageInSkillAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检查Buff(谁身上有什么buff,几层，比较符号)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1001,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比较符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20011,1,100,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检查属性，（谁身上，属性ID，值或者百分比（1整数，2百分比），值，比较符）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckBeActionInBeforeActionWheel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标前几息被调用了，是否包含当前息（1包含，0不包含）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckDamageType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSkillType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果是释放技能扳机就随便填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSkillKillingStyle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSkillFirstKeyType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断谁的技能是否是什么技能类型（1自己，2对方）（0不是，1是）（类型）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断谁的技能是否是杀式（1自己，2对方）（0不是，1是）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断技能首个键类型(1自己，2对方)（0不是，1是）(键类型)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断谁的攻击是什么伤害类型（1我自己攻击的类型，2对方攻击的类型）（0不是，1是）（类型）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSkillHasKeyType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断技能是否含有类型(1自己，2对方)（0没有，1有）(键类型)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckPropertyCompare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标1，属性ID1，目标2，属性ID2，比较符号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,2,2,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -87,7 +269,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,6 +284,34 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -126,8 +336,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -443,80 +659,344 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="27.25" customWidth="1"/>
-    <col min="6" max="6" width="41.25" customWidth="1"/>
+    <col min="1" max="2" width="9" style="2"/>
+    <col min="3" max="3" width="33.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32" style="1" customWidth="1"/>
+    <col min="5" max="5" width="80.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.75" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B4" s="2">
+        <v>10001</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B6" s="2">
+        <v>20001</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B8" s="2">
+        <v>30001</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
+      <c r="D8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B9" s="2">
+        <v>30101</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B11" s="2">
+        <v>40001</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B13" s="2">
+        <v>50101</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B14" s="2">
+        <v>50201</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B15" s="2">
+        <v>50301</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B16" s="2">
+        <v>50401</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B18" s="2">
+        <v>60001</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F49" s="2"/>
+    </row>
+    <row r="50" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F50" s="2"/>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F51" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91171438-25DC-4C1B-B230-0DEB57F2022F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28730E5A-94DF-44A7-A5A9-8C501E8555BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="4995" yWindow="4455" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -336,15 +336,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -666,8 +669,8 @@
     <col min="1" max="2" width="9" style="2"/>
     <col min="3" max="3" width="33.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="32" style="1" customWidth="1"/>
-    <col min="5" max="5" width="80.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.75" customWidth="1"/>
+    <col min="5" max="5" width="91.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.75" style="3" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>

--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28730E5A-94DF-44A7-A5A9-8C501E8555BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39495BB-1894-4041-B328-E9BEA74136F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4995" yWindow="4455" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="8895" yWindow="9900" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{C4206D52-59B6-491F-863D-BFDD0CF59D4B}">
+    <comment ref="H16" authorId="0" shapeId="0" xr:uid="{C4206D52-59B6-491F-863D-BFDD0CF59D4B}">
       <text>
         <r>
           <rPr>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="76">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -233,10 +233,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>判断谁的技能是否是杀式（1自己，2对方）（0不是，1是）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>判断技能首个键类型(1自己，2对方)（0不是，1是）(键类型)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -262,6 +258,146 @@
   </si>
   <si>
     <t>1,1,2,2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckBeDamageHpReduce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断（谁）是否扣血了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>800001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己是杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己不是杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断对方是杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断对方不是杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1200001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是单方面行动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是单向交锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是双向交锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1200002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1200003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckClashType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1200004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是交锋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -663,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -728,8 +864,8 @@
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B4" s="2">
-        <v>10001</v>
+      <c r="B4" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>19</v>
@@ -746,8 +882,8 @@
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B6" s="2">
-        <v>20001</v>
+      <c r="B6" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
@@ -764,8 +900,8 @@
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B8" s="2">
-        <v>30001</v>
+      <c r="B8" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
@@ -779,165 +915,261 @@
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="2">
-        <v>30101</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="2">
-        <v>40001</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="2">
-        <v>50101</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="2">
-        <v>50201</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B15" s="2">
-        <v>50301</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B16" s="2">
-        <v>50401</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="2"/>
-    </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="D17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B18" s="2">
-        <v>60001</v>
+      <c r="B18" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D24" s="2"/>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="F30" s="2"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B32" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.2">
@@ -996,6 +1228,27 @@
     </row>
     <row r="51" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F51" s="2"/>
+    </row>
+    <row r="52" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F52" s="2"/>
+    </row>
+    <row r="53" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F53" s="2"/>
+    </row>
+    <row r="54" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F54" s="2"/>
+    </row>
+    <row r="55" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F55" s="2"/>
+    </row>
+    <row r="56" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F56" s="2"/>
+    </row>
+    <row r="57" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F57" s="2"/>
+    </row>
+    <row r="58" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F58" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39495BB-1894-4041-B328-E9BEA74136F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{876BFF57-7125-4CDB-A9BB-0731D3DFCB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8895" yWindow="9900" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{31693E38-24A4-47D2-B27B-C8AB67E9FCF7}">
+    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{2E226496-D9A5-4D61-B9B0-354CC06D7148}">
       <text>
         <r>
           <rPr>
@@ -41,8 +41,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>Admin:
--2小于</t>
+          <t>Admin:</t>
         </r>
         <r>
           <rPr>
@@ -53,6 +52,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+-2小于
 -1小于等于
 0等于
 1大于等于
@@ -60,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H16" authorId="0" shapeId="0" xr:uid="{C4206D52-59B6-491F-863D-BFDD0CF59D4B}">
+    <comment ref="A46" authorId="0" shapeId="0" xr:uid="{4404A0BB-0684-415F-A1EE-932CF9B368D6}">
       <text>
         <r>
           <rPr>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="113">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -169,10 +169,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>判断谁技能期间是否被打了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CheckBeDamageInSkillAction</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -185,14 +181,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>比较符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,20011,1,100,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>检查属性，（谁身上，属性ID，值或者百分比（1整数，2百分比），值，比较符）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -217,10 +205,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>如果是释放技能扳机就随便填</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CheckSkillKillingStyle</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -237,10 +221,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>判断谁的攻击是什么伤害类型（1我自己攻击的类型，2对方攻击的类型）（0不是，1是）（类型）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CheckSkillHasKeyType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -265,10 +245,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>判断（谁）是否扣血了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>100001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -398,6 +374,178 @@
   </si>
   <si>
     <t>判断是交锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己的伤害类型不是直接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己的伤害类型是间接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己的伤害类型不是间接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,0,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己的伤害类型是直接伤害（1我自己攻击的类型，2对方攻击的类型）（0不是，1是）（类型）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断对方的伤害类型是直接伤害（1我自己攻击的类型，2对方攻击的类型）（0不是，1是）（类型）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断对方的伤害类型不是直接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断对方的伤害类型是间接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断对方的伤害类型不是间接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1300001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckMutualGoal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是否互为目标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1100002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己是否被破盾打到生命了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断对方是否被破盾打到生命了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己行动期间被打了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对方行动期间被打了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSkillTriggerMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断目标技能是否经过某个扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己当前技能是否经过行动后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身刚气大于等于50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20031,1,50,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断键数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1500001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckKeyCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,5,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己至少五个键</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -405,7 +553,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -449,13 +597,26 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -472,7 +633,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -483,6 +644,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -799,18 +963,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="33.75" style="2" customWidth="1"/>
+    <col min="1" max="1" width="29.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="2"/>
+    <col min="3" max="3" width="37.5" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32" style="1" customWidth="1"/>
     <col min="5" max="5" width="91.125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.75" style="3" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -827,7 +992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -845,7 +1010,7 @@
       </c>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -863,361 +1028,509 @@
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="2" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="D15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>22</v>
-      </c>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F16" s="2"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D25" s="2"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="D24" s="2"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="E26" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="F30" s="2"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B36" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B38" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="F38" s="2"/>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B39" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B40" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B41" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>94</v>
+      </c>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B43" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B45" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>108</v>
+      </c>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B47" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F48" s="2"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.2">
@@ -1249,6 +1562,33 @@
     </row>
     <row r="58" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F58" s="2"/>
+    </row>
+    <row r="59" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F59" s="2"/>
+    </row>
+    <row r="60" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F60" s="2"/>
+    </row>
+    <row r="61" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F61" s="2"/>
+    </row>
+    <row r="62" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F63" s="2"/>
+    </row>
+    <row r="64" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F64" s="2"/>
+    </row>
+    <row r="65" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F65" s="2"/>
+    </row>
+    <row r="66" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F66" s="2"/>
+    </row>
+    <row r="67" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F67" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{876BFF57-7125-4CDB-A9BB-0731D3DFCB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF6F63C-5ED3-4761-8B1D-12CE8440CE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -30,7 +39,7 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{2E226496-D9A5-4D61-B9B0-354CC06D7148}">
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{3E80E605-21CC-42D6-9E5B-891277957F25}">
       <text>
         <r>
           <rPr>
@@ -60,7 +69,277 @@
         </r>
       </text>
     </comment>
-    <comment ref="A46" authorId="0" shapeId="0" xr:uid="{4404A0BB-0684-415F-A1EE-932CF9B368D6}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{2E226496-D9A5-4D61-B9B0-354CC06D7148}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A13" authorId="0" shapeId="0" xr:uid="{88FFD23F-4770-4212-BDB4-E792A3027468}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A51" authorId="0" shapeId="0" xr:uid="{4404A0BB-0684-415F-A1EE-932CF9B368D6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A53" authorId="0" shapeId="0" xr:uid="{945C9952-661A-4999-8F70-73F1D7C63160}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A56" authorId="0" shapeId="0" xr:uid="{E5FC843F-DA07-43FF-AC47-ED46EFADEA7B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A58" authorId="0" shapeId="0" xr:uid="{F4E6CE43-F644-4C3B-ABDC-4422A791C047}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A60" authorId="0" shapeId="0" xr:uid="{C399D82A-C364-479A-A3EC-0765A1AC23FC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A62" authorId="0" shapeId="0" xr:uid="{1F66D5B5-D10B-4952-A6DF-EB0AD1CA976F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A63" authorId="0" shapeId="0" xr:uid="{85EC1931-B074-4549-93A0-AD9F25FEDB83}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A65" authorId="0" shapeId="0" xr:uid="{6CB726E4-43C1-43F0-9EA8-4B926C41E48E}">
       <text>
         <r>
           <rPr>
@@ -95,7 +374,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="160">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -177,10 +456,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,1001,1,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>检查属性，（谁身上，属性ID，值或者百分比（1整数，2百分比），值，比较符）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -237,10 +512,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,1,2,2,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CheckBeDamageHpReduce</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -269,10 +540,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>700001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>800001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -289,10 +556,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>700002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -305,22 +568,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>700003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>700004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>判断对方是杀式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>判断对方不是杀式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -546,6 +793,226 @@
   </si>
   <si>
     <t>自己至少五个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断交锋者是杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700040</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断交锋者不是杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,10041,6,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己身上是否大于等于6层迅速10041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1600001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSelfIsOppoTarget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己是否成为敌手的目标(一般配在行动决定后)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己是敌手的目标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己不是敌手的目标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1600000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断目标是杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断目标不是杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,30031,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1700001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckActionTimes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己的行动次数等于1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断上次使用某个招式是否被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckLastUseSkillIsBeCounter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己上次使用1022灵归招式是否被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1022,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18110221</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20341,5,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少有1层猊煞Buff30031</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少有5层毒瘴20341</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是否在第n息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1900001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckCurrActionWheel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,20031,1,40,-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标刚气低于40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20051,2,20031,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身玄气大于目标刚气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckDamageWithProperty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20071,1,0.8,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害大于等于自身技的80%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害与某个属性比较(目标，属性ID，1百分比，百分比值,比较符号)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害与某个属性比较(目标，属性ID，0值，比较符号)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckRandomSuccess</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机是否成功100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50概率成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2100050</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -963,13 +1430,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="76.125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="37.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="91.125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.75" style="3" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
@@ -1030,7 +1497,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
@@ -1039,556 +1506,736 @@
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>21</v>
+      <c r="B8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="D25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B28" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="D30" s="2"/>
       <c r="F30" s="2"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="F33" s="2"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B34" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="F34" s="2"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>96</v>
+        <v>75</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="F35" s="2"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>97</v>
+        <v>76</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="F36" s="2"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B37" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="F37" s="2"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="F38" s="2"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B39" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="F39" s="2"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>63</v>
+        <v>15</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="F40" s="2"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>69</v>
+        <v>51</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="F41" s="2"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="F42" s="2"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>93</v>
+        <v>58</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="F43" s="2"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
-        <v>103</v>
+      <c r="B44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F44" s="2"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B46" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B48" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F49" s="2"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B50" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F50" s="2"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F51" s="2"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B52" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E45" s="2" t="s">
+      <c r="D52" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="2"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F46" s="2"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B47" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F47" s="2"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F48" s="2"/>
-    </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F49" s="2"/>
-    </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F50" s="2"/>
-    </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F51" s="2"/>
-    </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F52" s="2"/>
     </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="F53" s="2"/>
     </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B54" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="F54" s="2"/>
     </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B55" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="F55" s="2"/>
     </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="F56" s="2"/>
     </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="F57" s="2"/>
     </row>
-    <row r="58" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="F58" s="2"/>
     </row>
-    <row r="59" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="F59" s="2"/>
     </row>
-    <row r="60" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>141</v>
+      </c>
       <c r="F60" s="2"/>
     </row>
-    <row r="61" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="F61" s="2"/>
     </row>
-    <row r="62" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="F62" s="2"/>
     </row>
-    <row r="63" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F63" s="2"/>
     </row>
-    <row r="64" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F64" s="2"/>
     </row>
-    <row r="65" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="F65" s="2"/>
     </row>
-    <row r="66" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B66" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>158</v>
+      </c>
       <c r="F66" s="2"/>
     </row>
-    <row r="67" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F67" s="2"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F68" s="2"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F69" s="2"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F70" s="2"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F71" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF6F63C-5ED3-4761-8B1D-12CE8440CE23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3647DC-E50E-4AF0-807D-7D416D53D6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -99,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A13" authorId="0" shapeId="0" xr:uid="{88FFD23F-4770-4212-BDB4-E792A3027468}">
+    <comment ref="A14" authorId="0" shapeId="0" xr:uid="{88FFD23F-4770-4212-BDB4-E792A3027468}">
       <text>
         <r>
           <rPr>
@@ -129,7 +129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A51" authorId="0" shapeId="0" xr:uid="{4404A0BB-0684-415F-A1EE-932CF9B368D6}">
+    <comment ref="A19" authorId="0" shapeId="0" xr:uid="{94C2B1DB-A662-4BC7-A851-8289F37F18C4}">
       <text>
         <r>
           <rPr>
@@ -159,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A53" authorId="0" shapeId="0" xr:uid="{945C9952-661A-4999-8F70-73F1D7C63160}">
+    <comment ref="A57" authorId="0" shapeId="0" xr:uid="{4404A0BB-0684-415F-A1EE-932CF9B368D6}">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A56" authorId="0" shapeId="0" xr:uid="{E5FC843F-DA07-43FF-AC47-ED46EFADEA7B}">
+    <comment ref="A59" authorId="0" shapeId="0" xr:uid="{945C9952-661A-4999-8F70-73F1D7C63160}">
       <text>
         <r>
           <rPr>
@@ -219,7 +219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A58" authorId="0" shapeId="0" xr:uid="{F4E6CE43-F644-4C3B-ABDC-4422A791C047}">
+    <comment ref="A62" authorId="0" shapeId="0" xr:uid="{E5FC843F-DA07-43FF-AC47-ED46EFADEA7B}">
       <text>
         <r>
           <rPr>
@@ -249,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A60" authorId="0" shapeId="0" xr:uid="{C399D82A-C364-479A-A3EC-0765A1AC23FC}">
+    <comment ref="A64" authorId="0" shapeId="0" xr:uid="{F4E6CE43-F644-4C3B-ABDC-4422A791C047}">
       <text>
         <r>
           <rPr>
@@ -279,7 +279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A62" authorId="0" shapeId="0" xr:uid="{1F66D5B5-D10B-4952-A6DF-EB0AD1CA976F}">
+    <comment ref="A66" authorId="0" shapeId="0" xr:uid="{C399D82A-C364-479A-A3EC-0765A1AC23FC}">
       <text>
         <r>
           <rPr>
@@ -309,7 +309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A63" authorId="0" shapeId="0" xr:uid="{85EC1931-B074-4549-93A0-AD9F25FEDB83}">
+    <comment ref="A68" authorId="0" shapeId="0" xr:uid="{1F66D5B5-D10B-4952-A6DF-EB0AD1CA976F}">
       <text>
         <r>
           <rPr>
@@ -339,7 +339,67 @@
         </r>
       </text>
     </comment>
-    <comment ref="A65" authorId="0" shapeId="0" xr:uid="{6CB726E4-43C1-43F0-9EA8-4B926C41E48E}">
+    <comment ref="A69" authorId="0" shapeId="0" xr:uid="{85EC1931-B074-4549-93A0-AD9F25FEDB83}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A71" authorId="0" shapeId="0" xr:uid="{6CB726E4-43C1-43F0-9EA8-4B926C41E48E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A73" authorId="0" shapeId="0" xr:uid="{48A947BE-D930-4648-AEEF-73C5E3E54577}">
       <text>
         <r>
           <rPr>
@@ -374,7 +434,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="183">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1013,6 +1073,98 @@
   </si>
   <si>
     <t>2100050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标1，BuffID1，目标2，BuffID2，比较符号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>410001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckBuffCompare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,20341,1,20341,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋者的毒瘴层数大于等于自身</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本回合是否行动过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckRoundAlreadyAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标，行动过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2200021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2200020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标，未行动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身刚气大于自身玄气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身刚气等于自身玄气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身刚气小于自身玄气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20031,1,20051,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20031,1,20051,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20031,1,20051,-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20051,1,35,-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身玄气小于等于35</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1430,7 +1582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="76.125" style="2" bestFit="1" customWidth="1"/>
@@ -1613,629 +1765,737 @@
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+      <c r="B13" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B14" s="2" t="s">
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B20" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B22" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B18" s="2" t="s">
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B20" s="2" t="s">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B26" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="2" t="s">
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B22" s="2" t="s">
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B28" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B23" s="2" t="s">
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B24" s="2" t="s">
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B30" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B31" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B27" s="2" t="s">
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B33" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="2" t="s">
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B35" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="D30" s="2"/>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B31" s="2" t="s">
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D36" s="2"/>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B37" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B32" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B33" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B34" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B35" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B36" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B39" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B40" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B41" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B43" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B44" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B40" s="2" t="s">
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B46" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F40" s="2"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B41" s="2" t="s">
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B47" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F41" s="2"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F42" s="2"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B43" s="2" t="s">
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B49" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E49" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="F43" s="2"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B44" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F44" s="2"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F45" s="2"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B46" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F46" s="2"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F47" s="2"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B48" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F48" s="2"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="F49" s="2"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="F50" s="2"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
-        <v>100</v>
+      <c r="B51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="F51" s="2"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="F52" s="2"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="F53" s="2"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F54" s="2"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F55" s="2"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B56" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F56" s="2"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F57" s="2"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F58" s="2"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F59" s="2"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="F54" s="2"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B55" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F55" s="2"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F56" s="2"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F57" s="2"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="F58" s="2"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B59" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F59" s="2"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="F60" s="2"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="E61" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="F61" s="2"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B63" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F63" s="2"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F64" s="2"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B65" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F65" s="2"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F66" s="2"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B67" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F67" s="2"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F62" s="2"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="4" t="s">
+      <c r="F68" s="2"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B69" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E69" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F63" s="2"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F64" s="2"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="F65" s="2"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B66" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F66" s="2"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F67" s="2"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F68" s="2"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F69" s="2"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F70" s="2"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="F71" s="2"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B72" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F72" s="2"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F73" s="2"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B74" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F74" s="2"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B75" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F75" s="2"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F76" s="2"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F77" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3647DC-E50E-4AF0-807D-7D416D53D6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B19D0B1-0807-4373-9973-A9CBE68B46C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -159,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A57" authorId="0" shapeId="0" xr:uid="{4404A0BB-0684-415F-A1EE-932CF9B368D6}">
+    <comment ref="A60" authorId="0" shapeId="0" xr:uid="{4404A0BB-0684-415F-A1EE-932CF9B368D6}">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A59" authorId="0" shapeId="0" xr:uid="{945C9952-661A-4999-8F70-73F1D7C63160}">
+    <comment ref="A62" authorId="0" shapeId="0" xr:uid="{945C9952-661A-4999-8F70-73F1D7C63160}">
       <text>
         <r>
           <rPr>
@@ -219,7 +219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A62" authorId="0" shapeId="0" xr:uid="{E5FC843F-DA07-43FF-AC47-ED46EFADEA7B}">
+    <comment ref="A65" authorId="0" shapeId="0" xr:uid="{E5FC843F-DA07-43FF-AC47-ED46EFADEA7B}">
       <text>
         <r>
           <rPr>
@@ -249,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A64" authorId="0" shapeId="0" xr:uid="{F4E6CE43-F644-4C3B-ABDC-4422A791C047}">
+    <comment ref="A68" authorId="0" shapeId="0" xr:uid="{F4E6CE43-F644-4C3B-ABDC-4422A791C047}">
       <text>
         <r>
           <rPr>
@@ -279,7 +279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A66" authorId="0" shapeId="0" xr:uid="{C399D82A-C364-479A-A3EC-0765A1AC23FC}">
+    <comment ref="A70" authorId="0" shapeId="0" xr:uid="{C399D82A-C364-479A-A3EC-0765A1AC23FC}">
       <text>
         <r>
           <rPr>
@@ -309,7 +309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A68" authorId="0" shapeId="0" xr:uid="{1F66D5B5-D10B-4952-A6DF-EB0AD1CA976F}">
+    <comment ref="A72" authorId="0" shapeId="0" xr:uid="{1F66D5B5-D10B-4952-A6DF-EB0AD1CA976F}">
       <text>
         <r>
           <rPr>
@@ -339,7 +339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A69" authorId="0" shapeId="0" xr:uid="{85EC1931-B074-4549-93A0-AD9F25FEDB83}">
+    <comment ref="A73" authorId="0" shapeId="0" xr:uid="{85EC1931-B074-4549-93A0-AD9F25FEDB83}">
       <text>
         <r>
           <rPr>
@@ -369,7 +369,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A71" authorId="0" shapeId="0" xr:uid="{6CB726E4-43C1-43F0-9EA8-4B926C41E48E}">
+    <comment ref="A78" authorId="0" shapeId="0" xr:uid="{6CB726E4-43C1-43F0-9EA8-4B926C41E48E}">
       <text>
         <r>
           <rPr>
@@ -399,7 +399,277 @@
         </r>
       </text>
     </comment>
-    <comment ref="A73" authorId="0" shapeId="0" xr:uid="{48A947BE-D930-4648-AEEF-73C5E3E54577}">
+    <comment ref="A80" authorId="0" shapeId="0" xr:uid="{48A947BE-D930-4648-AEEF-73C5E3E54577}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A83" authorId="0" shapeId="0" xr:uid="{FFA67B4A-F5E9-410C-B978-FA21684F4A99}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A85" authorId="0" shapeId="0" xr:uid="{C34EDA1F-45FF-465B-8605-9DF11F149AB5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A88" authorId="0" shapeId="0" xr:uid="{3C5CD11B-F2CA-45A2-BE89-D1E9F21EB1DF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A92" authorId="0" shapeId="0" xr:uid="{CA1902F7-A507-4529-AA72-0F8B32376739}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A94" authorId="0" shapeId="0" xr:uid="{218E0718-1A2C-40C8-96DD-53C5CEBF5930}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A96" authorId="0" shapeId="0" xr:uid="{E8FCF4D6-C27A-404E-9297-2D9C6DC5F649}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A99" authorId="0" shapeId="0" xr:uid="{7B8DA6B6-B8CE-4E4B-A708-BB9B30194380}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A101" authorId="0" shapeId="0" xr:uid="{6C7FF865-48A1-4DF1-8E66-09049149C8DF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A103" authorId="0" shapeId="0" xr:uid="{E1905A74-2E51-4936-9C51-A4FAFD9A81F5}">
       <text>
         <r>
           <rPr>
@@ -434,7 +704,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="263">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -560,10 +830,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>判断技能是否含有类型(1自己，2对方)（0没有，1有）(键类型)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CheckPropertyCompare</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -604,10 +870,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>900001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1000001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -948,14 +1210,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1700001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>判断行动次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CheckActionTimes</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1165,6 +1419,342 @@
   </si>
   <si>
     <t>自身玄气小于等于35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>410002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,20341,1,20341,-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标毒瘴小于自身</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断种类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckVariety</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标是否是鬼物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2300023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckNowRoundUsedPowerKilling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckNowRoundUsedArtrKilling</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断技能使用状况(目标)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己本回合是否使用过武杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己本回合是否使用过术杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2400002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2500001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckBuffTypeCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,0,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断buff种类数量(目标，类型，比较值，比较符号)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身异常buff数量大于0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2600001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断本回合受到直接伤害的次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本回合受到直接伤害次数少于两次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckRoundBeDirectDamageTimes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断目标有几个不同的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2700013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckNoSameKeyCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己是否有三种不同的键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>992032</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少持有2个相同的键与1个不相同的键时可使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSkillCondition2033</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2500002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,0,-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身异常buff数量小于等于0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断目标是否是首次行动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckIsFirstAction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己是首次行动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2800011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2800010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己不是首次行动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断目标是否带有某类留劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckTargetHasArrowBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2900410</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋者未带有↑类留劲状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckRoundBeSameDirectDamaged</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000121</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckRoundBeDirectKillAttack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断目标本回合是否受到过杀式直接攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断目标是否受到过目标的直接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己受到过目标的直接伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己未受到过杀式直接攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3100100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,2,-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身异常buff数量小于等于2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2500003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>410003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>410004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20341,4,20341,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身的毒瘴层数大于交锋者的层数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋者的毒瘴层数大于自身的层数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,20341,1,20341,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对方技能没有↑键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断目标技能是否含有某个键(目标，关系，键类型)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害大于等于自身力的80%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20061,1,0.8,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害大于等于自身力的100%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20061,1,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断行动次数(目标,次数,比较符号)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1700110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1700200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标的行动次数等于0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20061,1,0.55,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害大于等于自身力的55%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1582,10 +2172,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="76.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="37.5" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.625" style="1" customWidth="1"/>
@@ -1649,7 +2239,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
@@ -1658,22 +2248,22 @@
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -1685,46 +2275,46 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -1736,766 +2326,1108 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B21" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>181</v>
+      </c>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>39</v>
+        <v>239</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B24" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B26" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B28" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>124</v>
+        <v>44</v>
       </c>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="F30" s="2"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B32" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B34" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B38" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D39" s="2"/>
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B40" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="D36" s="2"/>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B38" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B39" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B40" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B45" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>88</v>
+        <v>75</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>89</v>
+        <v>76</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F48" s="2"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>53</v>
+      <c r="E49" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="F49" s="2"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="F50" s="2"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="F51" s="2"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F52" s="2"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
-        <v>86</v>
+      <c r="B53" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="F53" s="2"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F54" s="2"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F55" s="2"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F54" s="2"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
+      <c r="F56" s="2"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F57" s="2"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F58" s="2"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F55" s="2"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B56" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="E59" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F56" s="2"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F57" s="2"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B58" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F58" s="2"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
-        <v>117</v>
-      </c>
       <c r="F59" s="2"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B60" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>119</v>
+      <c r="A60" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="F60" s="2"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="F61" s="2"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="F62" s="2"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F63" s="2"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="4" t="s">
-        <v>132</v>
+      <c r="B64" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="F64" s="2"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B65" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>134</v>
+      <c r="A65" s="4" t="s">
+        <v>254</v>
       </c>
       <c r="F65" s="2"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="4" t="s">
-        <v>141</v>
+      <c r="B66" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="F66" s="2"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="2" t="s">
-        <v>142</v>
+        <v>257</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>15</v>
+        <v>256</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>258</v>
       </c>
       <c r="F67" s="2"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="F68" s="2"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="4" t="s">
-        <v>154</v>
-      </c>
       <c r="B69" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F69" s="2"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F70" s="2"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B71" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F71" s="2"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F69" s="2"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F70" s="2"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="F71" s="2"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B72" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="F72" s="2"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="F73" s="2"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B74" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>48</v>
+        <v>147</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="F74" s="2"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B75" s="2" t="s">
-        <v>169</v>
+        <v>248</v>
       </c>
       <c r="C75" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F75" s="2"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B76" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F76" s="2"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B77" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F77" s="2"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F78" s="2"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B79" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F79" s="2"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F80" s="2"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B81" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F81" s="2"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B82" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F75" s="2"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F76" s="2"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F77" s="2"/>
+      <c r="F82" s="2"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F83" s="2"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B84" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F84" s="2"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B86" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B87" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B89" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B90" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B91" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B93" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B95" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B97" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B98" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B100" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B102" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B104" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B106" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>210</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B19D0B1-0807-4373-9973-A9CBE68B46C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56A52D1-4FE5-4F67-839E-1373BD9CA6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -69,7 +69,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{2E226496-D9A5-4D61-B9B0-354CC06D7148}">
+    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{2E226496-D9A5-4D61-B9B0-354CC06D7148}">
       <text>
         <r>
           <rPr>
@@ -99,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A14" authorId="0" shapeId="0" xr:uid="{88FFD23F-4770-4212-BDB4-E792A3027468}">
+    <comment ref="A16" authorId="0" shapeId="0" xr:uid="{88FFD23F-4770-4212-BDB4-E792A3027468}">
       <text>
         <r>
           <rPr>
@@ -129,7 +129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A19" authorId="0" shapeId="0" xr:uid="{94C2B1DB-A662-4BC7-A851-8289F37F18C4}">
+    <comment ref="A22" authorId="0" shapeId="0" xr:uid="{94C2B1DB-A662-4BC7-A851-8289F37F18C4}">
       <text>
         <r>
           <rPr>
@@ -159,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A60" authorId="0" shapeId="0" xr:uid="{4404A0BB-0684-415F-A1EE-932CF9B368D6}">
+    <comment ref="A63" authorId="0" shapeId="0" xr:uid="{4404A0BB-0684-415F-A1EE-932CF9B368D6}">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A62" authorId="0" shapeId="0" xr:uid="{945C9952-661A-4999-8F70-73F1D7C63160}">
+    <comment ref="A66" authorId="0" shapeId="0" xr:uid="{945C9952-661A-4999-8F70-73F1D7C63160}">
       <text>
         <r>
           <rPr>
@@ -219,7 +219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A65" authorId="0" shapeId="0" xr:uid="{E5FC843F-DA07-43FF-AC47-ED46EFADEA7B}">
+    <comment ref="A69" authorId="0" shapeId="0" xr:uid="{E5FC843F-DA07-43FF-AC47-ED46EFADEA7B}">
       <text>
         <r>
           <rPr>
@@ -249,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A68" authorId="0" shapeId="0" xr:uid="{F4E6CE43-F644-4C3B-ABDC-4422A791C047}">
+    <comment ref="A72" authorId="0" shapeId="0" xr:uid="{F4E6CE43-F644-4C3B-ABDC-4422A791C047}">
       <text>
         <r>
           <rPr>
@@ -279,7 +279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A70" authorId="0" shapeId="0" xr:uid="{C399D82A-C364-479A-A3EC-0765A1AC23FC}">
+    <comment ref="A74" authorId="0" shapeId="0" xr:uid="{C399D82A-C364-479A-A3EC-0765A1AC23FC}">
       <text>
         <r>
           <rPr>
@@ -309,7 +309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A72" authorId="0" shapeId="0" xr:uid="{1F66D5B5-D10B-4952-A6DF-EB0AD1CA976F}">
+    <comment ref="A77" authorId="0" shapeId="0" xr:uid="{1F66D5B5-D10B-4952-A6DF-EB0AD1CA976F}">
       <text>
         <r>
           <rPr>
@@ -339,7 +339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A73" authorId="0" shapeId="0" xr:uid="{85EC1931-B074-4549-93A0-AD9F25FEDB83}">
+    <comment ref="A78" authorId="0" shapeId="0" xr:uid="{85EC1931-B074-4549-93A0-AD9F25FEDB83}">
       <text>
         <r>
           <rPr>
@@ -369,7 +369,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A78" authorId="0" shapeId="0" xr:uid="{6CB726E4-43C1-43F0-9EA8-4B926C41E48E}">
+    <comment ref="A83" authorId="0" shapeId="0" xr:uid="{6CB726E4-43C1-43F0-9EA8-4B926C41E48E}">
       <text>
         <r>
           <rPr>
@@ -399,7 +399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A80" authorId="0" shapeId="0" xr:uid="{48A947BE-D930-4648-AEEF-73C5E3E54577}">
+    <comment ref="A85" authorId="0" shapeId="0" xr:uid="{48A947BE-D930-4648-AEEF-73C5E3E54577}">
       <text>
         <r>
           <rPr>
@@ -429,7 +429,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A83" authorId="0" shapeId="0" xr:uid="{FFA67B4A-F5E9-410C-B978-FA21684F4A99}">
+    <comment ref="A88" authorId="0" shapeId="0" xr:uid="{FFA67B4A-F5E9-410C-B978-FA21684F4A99}">
       <text>
         <r>
           <rPr>
@@ -459,7 +459,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A85" authorId="0" shapeId="0" xr:uid="{C34EDA1F-45FF-465B-8605-9DF11F149AB5}">
+    <comment ref="A90" authorId="0" shapeId="0" xr:uid="{C34EDA1F-45FF-465B-8605-9DF11F149AB5}">
       <text>
         <r>
           <rPr>
@@ -489,7 +489,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A88" authorId="0" shapeId="0" xr:uid="{3C5CD11B-F2CA-45A2-BE89-D1E9F21EB1DF}">
+    <comment ref="A93" authorId="0" shapeId="0" xr:uid="{3C5CD11B-F2CA-45A2-BE89-D1E9F21EB1DF}">
       <text>
         <r>
           <rPr>
@@ -519,7 +519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A92" authorId="0" shapeId="0" xr:uid="{CA1902F7-A507-4529-AA72-0F8B32376739}">
+    <comment ref="A97" authorId="0" shapeId="0" xr:uid="{CA1902F7-A507-4529-AA72-0F8B32376739}">
       <text>
         <r>
           <rPr>
@@ -549,7 +549,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A94" authorId="0" shapeId="0" xr:uid="{218E0718-1A2C-40C8-96DD-53C5CEBF5930}">
+    <comment ref="A99" authorId="0" shapeId="0" xr:uid="{218E0718-1A2C-40C8-96DD-53C5CEBF5930}">
       <text>
         <r>
           <rPr>
@@ -579,7 +579,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A96" authorId="0" shapeId="0" xr:uid="{E8FCF4D6-C27A-404E-9297-2D9C6DC5F649}">
+    <comment ref="A101" authorId="0" shapeId="0" xr:uid="{E8FCF4D6-C27A-404E-9297-2D9C6DC5F649}">
       <text>
         <r>
           <rPr>
@@ -609,7 +609,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A99" authorId="0" shapeId="0" xr:uid="{7B8DA6B6-B8CE-4E4B-A708-BB9B30194380}">
+    <comment ref="A104" authorId="0" shapeId="0" xr:uid="{7B8DA6B6-B8CE-4E4B-A708-BB9B30194380}">
       <text>
         <r>
           <rPr>
@@ -639,7 +639,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A101" authorId="0" shapeId="0" xr:uid="{6C7FF865-48A1-4DF1-8E66-09049149C8DF}">
+    <comment ref="A106" authorId="0" shapeId="0" xr:uid="{6C7FF865-48A1-4DF1-8E66-09049149C8DF}">
       <text>
         <r>
           <rPr>
@@ -669,7 +669,127 @@
         </r>
       </text>
     </comment>
-    <comment ref="A103" authorId="0" shapeId="0" xr:uid="{E1905A74-2E51-4936-9C51-A4FAFD9A81F5}">
+    <comment ref="A108" authorId="0" shapeId="0" xr:uid="{E1905A74-2E51-4936-9C51-A4FAFD9A81F5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A110" authorId="0" shapeId="0" xr:uid="{343ABA23-0C71-4DD9-9526-D659AE92536E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A112" authorId="0" shapeId="0" xr:uid="{91D3FFAD-AAB8-4AE8-A0E7-42FFED952D55}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A125" authorId="0" shapeId="0" xr:uid="{0C9DF881-3498-4E87-9087-181B115A5E71}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A134" authorId="0" shapeId="0" xr:uid="{63285060-972C-4852-9EDD-206CF2B2818F}">
       <text>
         <r>
           <rPr>
@@ -704,7 +824,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="347">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1154,10 +1274,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自己身上是否大于等于6层迅速10041</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1600001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1242,14 +1358,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>至少有1层猊煞Buff30031</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>至少有5层毒瘴20341</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>200003</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1755,6 +1863,338 @@
   </si>
   <si>
     <t>造成的伤害大于等于自身力的55%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,20011,1,20011,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标体大于自身体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身至少有1层猊煞Buff30031</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身身上是否大于等于6层迅速10041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身至少有5层毒瘴20341</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,30371,0,-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身没有兽化身30371</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckTargetHasAvatarBuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断目标是否化身类buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3200001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己有化身类buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,30381,0,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身至少有1层禽化身30381</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1500002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己键小于3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断时刻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3300001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckChrono</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是日出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3300002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3300003</t>
+  </si>
+  <si>
+    <t>3300004</t>
+  </si>
+  <si>
+    <t>3300005</t>
+  </si>
+  <si>
+    <t>3300006</t>
+  </si>
+  <si>
+    <t>3300007</t>
+  </si>
+  <si>
+    <t>3300008</t>
+  </si>
+  <si>
+    <t>3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是早晨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是日落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是夜晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断不是日出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断不是夜晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断不是日落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断不是早晨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3300010</t>
+  </si>
+  <si>
+    <t>3300011</t>
+  </si>
+  <si>
+    <t>3300012</t>
+  </si>
+  <si>
+    <t>5,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是昼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断不是昼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是夜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断不是夜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断天气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3400001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3400002</t>
+  </si>
+  <si>
+    <t>3400003</t>
+  </si>
+  <si>
+    <t>3400004</t>
+  </si>
+  <si>
+    <t>3400005</t>
+  </si>
+  <si>
+    <t>3400006</t>
+  </si>
+  <si>
+    <t>3400007</t>
+  </si>
+  <si>
+    <t>3400008</t>
+  </si>
+  <si>
+    <t>CheckWeather</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断不是晴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是阴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断不是阴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断不是雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是雾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断不是雾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断是晴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3300009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断上次技能交锋结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckSkillLastClashState</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3083,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断上次释放移祸3083是否存在交锋失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35130830</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35130990</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35131040</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3099,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3104,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断上次释放移祸3099是否存在交锋失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断上次释放移祸3104是否存在交锋失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35131140</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3114,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断上次释放3114是否存在交锋失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1900002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不在第0息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在第1息</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1842,7 +2282,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1857,6 +2297,9 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2172,11 +2615,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9" style="2"/>
+    <col min="2" max="2" width="10.75" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.5" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="91.125" style="2" bestFit="1" customWidth="1"/>
@@ -2284,545 +2727,557 @@
         <v>111</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>112</v>
+        <v>265</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>134</v>
+        <v>264</v>
       </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>135</v>
+        <v>266</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>20</v>
+      <c r="B10" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>268</v>
       </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>273</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>97</v>
+        <v>274</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>142</v>
+      <c r="A12" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>176</v>
+        <v>36</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>32</v>
+      <c r="B14" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>37</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B16" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>170</v>
+      <c r="A16" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
-        <v>156</v>
+      <c r="B19" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>158</v>
+        <v>31</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>158</v>
+        <v>31</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>181</v>
+        <v>262</v>
       </c>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B22" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>242</v>
+      <c r="A22" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>240</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>244</v>
+        <v>156</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>243</v>
+        <v>157</v>
       </c>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B24" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>178</v>
+      </c>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B26" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B28" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B27" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="F30" s="2"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B31" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="F33" s="2"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F34" s="2"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B35" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="F35" s="2"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B37" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B39" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B38" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D39" s="2"/>
       <c r="F39" s="2"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B40" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>77</v>
+      <c r="A40" s="4" t="s">
+        <v>244</v>
       </c>
       <c r="F40" s="2"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>60</v>
+        <v>243</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>67</v>
+        <v>242</v>
       </c>
       <c r="F41" s="2"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B42" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="D42" s="2"/>
       <c r="F42" s="2"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F43" s="2"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F44" s="2"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F45" s="2"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F46" s="2"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F47" s="2"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B48" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="F48" s="2"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="F49" s="2"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>87</v>
+        <v>76</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -2831,602 +3286,1038 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>51</v>
+      <c r="E52" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="F52" s="2"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>52</v>
+      <c r="E53" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="F53" s="2"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B54" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="F54" s="2"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F55" s="2"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
-        <v>84</v>
+      <c r="B56" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="F56" s="2"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F57" s="2"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F58" s="2"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F59" s="2"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F57" s="2"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
+      <c r="F60" s="2"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F58" s="2"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B59" s="2" t="s">
+      <c r="F61" s="2"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B62" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E62" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F59" s="2"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="4" t="s">
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="F60" s="2"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B61" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F61" s="2"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F62" s="2"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B63" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="F63" s="2"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B64" s="2" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C64" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F64" s="2"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B65" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F65" s="2"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F64" s="2"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="F65" s="2"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B66" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="F66" s="2"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="2" t="s">
-        <v>257</v>
+        <v>118</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F67" s="2"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B68" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F68" s="2"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F69" s="2"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B70" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F67" s="2"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F68" s="2"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B69" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F69" s="2"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="F70" s="2"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B71" s="2" t="s">
-        <v>138</v>
+        <v>254</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>15</v>
+        <v>253</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>255</v>
       </c>
       <c r="F71" s="2"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="F72" s="2"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="4" t="s">
-        <v>150</v>
+      <c r="B73" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F73" s="2"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B74" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>148</v>
+      <c r="A74" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="F74" s="2"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B75" s="2" t="s">
-        <v>248</v>
+        <v>135</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>252</v>
+        <v>16</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>251</v>
+        <v>346</v>
       </c>
       <c r="F75" s="2"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B76" s="2" t="s">
-        <v>259</v>
+        <v>343</v>
       </c>
       <c r="C76" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F76" s="2"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F76" s="2"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B77" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>262</v>
       </c>
       <c r="F77" s="2"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F78" s="2"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B79" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F79" s="2"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="4" t="s">
-        <v>161</v>
+      <c r="B80" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="F80" s="2"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B81" s="2" t="s">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>46</v>
+        <v>247</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>163</v>
+        <v>246</v>
       </c>
       <c r="F81" s="2"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B82" s="2" t="s">
-        <v>165</v>
+        <v>257</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>47</v>
+        <v>258</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>166</v>
+        <v>259</v>
       </c>
       <c r="F82" s="2"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
       <c r="F83" s="2"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B84" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="F84" s="2"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>190</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="F85" s="2"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B86" s="2" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>191</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="F86" s="2"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B87" s="2" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>192</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="F87" s="2"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>197</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="F88" s="2"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B89" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>198</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="F89" s="2"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B90" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>214</v>
+      <c r="A90" s="4" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B91" s="2" t="s">
-        <v>238</v>
+        <v>184</v>
       </c>
       <c r="C91" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B92" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B94" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A92" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B93" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A94" s="4" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B95" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A96" s="4" t="s">
-        <v>215</v>
+      <c r="B96" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B97" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>217</v>
+      <c r="A97" s="4" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B98" s="2" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>43</v>
+        <v>198</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B100" s="2" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B102" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B103" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B105" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="C102" s="2" t="s">
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B107" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B109" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A103" s="4" t="s">
+      <c r="D109" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B104" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B106" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>210</v>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B111" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B113" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B114" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B115" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B116" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B117" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B118" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B119" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B120" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B121" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B122" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B123" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B124" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B126" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B127" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B128" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B129" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B130" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B131" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B132" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B133" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A134" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B135" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B136" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B137" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B138" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B140" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56A52D1-4FE5-4F67-839E-1373BD9CA6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E133DC30-2AEB-480B-8C55-2411E84D0A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="345" yWindow="5700" windowWidth="35565" windowHeight="14115" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -819,12 +819,42 @@
         </r>
       </text>
     </comment>
+    <comment ref="A139" authorId="0" shapeId="0" xr:uid="{649C4F38-1020-4339-86B1-D2195E611C1D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="351">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2195,6 +2225,22 @@
   </si>
   <si>
     <t>在第1息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首次造成击破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckFirstKill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能首次造成击破</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2615,7 +2661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38.125" style="2" customWidth="1"/>
@@ -4309,14 +4355,30 @@
         <v>342</v>
       </c>
     </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B140" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B142" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="C142" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E140" s="2" t="s">
+      <c r="E142" s="2" t="s">
         <v>207</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E133DC30-2AEB-480B-8C55-2411E84D0A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76552D05-F9DE-49E9-AA4D-34556A3488A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="5700" windowWidth="35565" windowHeight="14115" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView minimized="1" xWindow="4215" yWindow="6120" windowWidth="35565" windowHeight="9315" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{2E226496-D9A5-4D61-B9B0-354CC06D7148}">
+    <comment ref="A13" authorId="0" shapeId="0" xr:uid="{2E226496-D9A5-4D61-B9B0-354CC06D7148}">
       <text>
         <r>
           <rPr>
@@ -99,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A16" authorId="0" shapeId="0" xr:uid="{88FFD23F-4770-4212-BDB4-E792A3027468}">
+    <comment ref="A17" authorId="0" shapeId="0" xr:uid="{88FFD23F-4770-4212-BDB4-E792A3027468}">
       <text>
         <r>
           <rPr>
@@ -129,7 +129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A22" authorId="0" shapeId="0" xr:uid="{94C2B1DB-A662-4BC7-A851-8289F37F18C4}">
+    <comment ref="A23" authorId="0" shapeId="0" xr:uid="{94C2B1DB-A662-4BC7-A851-8289F37F18C4}">
       <text>
         <r>
           <rPr>
@@ -159,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A63" authorId="0" shapeId="0" xr:uid="{4404A0BB-0684-415F-A1EE-932CF9B368D6}">
+    <comment ref="A73" authorId="0" shapeId="0" xr:uid="{4404A0BB-0684-415F-A1EE-932CF9B368D6}">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A66" authorId="0" shapeId="0" xr:uid="{945C9952-661A-4999-8F70-73F1D7C63160}">
+    <comment ref="A76" authorId="0" shapeId="0" xr:uid="{945C9952-661A-4999-8F70-73F1D7C63160}">
       <text>
         <r>
           <rPr>
@@ -219,7 +219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A69" authorId="0" shapeId="0" xr:uid="{E5FC843F-DA07-43FF-AC47-ED46EFADEA7B}">
+    <comment ref="A79" authorId="0" shapeId="0" xr:uid="{E5FC843F-DA07-43FF-AC47-ED46EFADEA7B}">
       <text>
         <r>
           <rPr>
@@ -249,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A72" authorId="0" shapeId="0" xr:uid="{F4E6CE43-F644-4C3B-ABDC-4422A791C047}">
+    <comment ref="A82" authorId="0" shapeId="0" xr:uid="{F4E6CE43-F644-4C3B-ABDC-4422A791C047}">
       <text>
         <r>
           <rPr>
@@ -279,7 +279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A74" authorId="0" shapeId="0" xr:uid="{C399D82A-C364-479A-A3EC-0765A1AC23FC}">
+    <comment ref="A84" authorId="0" shapeId="0" xr:uid="{C399D82A-C364-479A-A3EC-0765A1AC23FC}">
       <text>
         <r>
           <rPr>
@@ -309,7 +309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A77" authorId="0" shapeId="0" xr:uid="{1F66D5B5-D10B-4952-A6DF-EB0AD1CA976F}">
+    <comment ref="A87" authorId="0" shapeId="0" xr:uid="{1F66D5B5-D10B-4952-A6DF-EB0AD1CA976F}">
       <text>
         <r>
           <rPr>
@@ -339,7 +339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A78" authorId="0" shapeId="0" xr:uid="{85EC1931-B074-4549-93A0-AD9F25FEDB83}">
+    <comment ref="A88" authorId="0" shapeId="0" xr:uid="{85EC1931-B074-4549-93A0-AD9F25FEDB83}">
       <text>
         <r>
           <rPr>
@@ -369,7 +369,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A83" authorId="0" shapeId="0" xr:uid="{6CB726E4-43C1-43F0-9EA8-4B926C41E48E}">
+    <comment ref="A93" authorId="0" shapeId="0" xr:uid="{6CB726E4-43C1-43F0-9EA8-4B926C41E48E}">
       <text>
         <r>
           <rPr>
@@ -399,7 +399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A85" authorId="0" shapeId="0" xr:uid="{48A947BE-D930-4648-AEEF-73C5E3E54577}">
+    <comment ref="A95" authorId="0" shapeId="0" xr:uid="{48A947BE-D930-4648-AEEF-73C5E3E54577}">
       <text>
         <r>
           <rPr>
@@ -429,7 +429,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A88" authorId="0" shapeId="0" xr:uid="{FFA67B4A-F5E9-410C-B978-FA21684F4A99}">
+    <comment ref="A98" authorId="0" shapeId="0" xr:uid="{FFA67B4A-F5E9-410C-B978-FA21684F4A99}">
       <text>
         <r>
           <rPr>
@@ -459,7 +459,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A90" authorId="0" shapeId="0" xr:uid="{C34EDA1F-45FF-465B-8605-9DF11F149AB5}">
+    <comment ref="A100" authorId="0" shapeId="0" xr:uid="{C34EDA1F-45FF-465B-8605-9DF11F149AB5}">
       <text>
         <r>
           <rPr>
@@ -489,7 +489,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A93" authorId="0" shapeId="0" xr:uid="{3C5CD11B-F2CA-45A2-BE89-D1E9F21EB1DF}">
+    <comment ref="A103" authorId="0" shapeId="0" xr:uid="{3C5CD11B-F2CA-45A2-BE89-D1E9F21EB1DF}">
       <text>
         <r>
           <rPr>
@@ -519,7 +519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A97" authorId="0" shapeId="0" xr:uid="{CA1902F7-A507-4529-AA72-0F8B32376739}">
+    <comment ref="A107" authorId="0" shapeId="0" xr:uid="{CA1902F7-A507-4529-AA72-0F8B32376739}">
       <text>
         <r>
           <rPr>
@@ -549,7 +549,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A99" authorId="0" shapeId="0" xr:uid="{218E0718-1A2C-40C8-96DD-53C5CEBF5930}">
+    <comment ref="A109" authorId="0" shapeId="0" xr:uid="{218E0718-1A2C-40C8-96DD-53C5CEBF5930}">
       <text>
         <r>
           <rPr>
@@ -579,7 +579,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A101" authorId="0" shapeId="0" xr:uid="{E8FCF4D6-C27A-404E-9297-2D9C6DC5F649}">
+    <comment ref="A111" authorId="0" shapeId="0" xr:uid="{E8FCF4D6-C27A-404E-9297-2D9C6DC5F649}">
       <text>
         <r>
           <rPr>
@@ -609,7 +609,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A104" authorId="0" shapeId="0" xr:uid="{7B8DA6B6-B8CE-4E4B-A708-BB9B30194380}">
+    <comment ref="A114" authorId="0" shapeId="0" xr:uid="{7B8DA6B6-B8CE-4E4B-A708-BB9B30194380}">
       <text>
         <r>
           <rPr>
@@ -639,7 +639,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A106" authorId="0" shapeId="0" xr:uid="{6C7FF865-48A1-4DF1-8E66-09049149C8DF}">
+    <comment ref="A116" authorId="0" shapeId="0" xr:uid="{6C7FF865-48A1-4DF1-8E66-09049149C8DF}">
       <text>
         <r>
           <rPr>
@@ -669,7 +669,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A108" authorId="0" shapeId="0" xr:uid="{E1905A74-2E51-4936-9C51-A4FAFD9A81F5}">
+    <comment ref="A118" authorId="0" shapeId="0" xr:uid="{E1905A74-2E51-4936-9C51-A4FAFD9A81F5}">
       <text>
         <r>
           <rPr>
@@ -699,7 +699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A110" authorId="0" shapeId="0" xr:uid="{343ABA23-0C71-4DD9-9526-D659AE92536E}">
+    <comment ref="A120" authorId="0" shapeId="0" xr:uid="{343ABA23-0C71-4DD9-9526-D659AE92536E}">
       <text>
         <r>
           <rPr>
@@ -729,7 +729,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A112" authorId="0" shapeId="0" xr:uid="{91D3FFAD-AAB8-4AE8-A0E7-42FFED952D55}">
+    <comment ref="A122" authorId="0" shapeId="0" xr:uid="{91D3FFAD-AAB8-4AE8-A0E7-42FFED952D55}">
       <text>
         <r>
           <rPr>
@@ -759,7 +759,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A125" authorId="0" shapeId="0" xr:uid="{0C9DF881-3498-4E87-9087-181B115A5E71}">
+    <comment ref="A135" authorId="0" shapeId="0" xr:uid="{0C9DF881-3498-4E87-9087-181B115A5E71}">
       <text>
         <r>
           <rPr>
@@ -789,7 +789,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A134" authorId="0" shapeId="0" xr:uid="{63285060-972C-4852-9EDD-206CF2B2818F}">
+    <comment ref="A144" authorId="0" shapeId="0" xr:uid="{63285060-972C-4852-9EDD-206CF2B2818F}">
       <text>
         <r>
           <rPr>
@@ -819,7 +819,127 @@
         </r>
       </text>
     </comment>
-    <comment ref="A139" authorId="0" shapeId="0" xr:uid="{649C4F38-1020-4339-86B1-D2195E611C1D}">
+    <comment ref="A149" authorId="0" shapeId="0" xr:uid="{649C4F38-1020-4339-86B1-D2195E611C1D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A151" authorId="0" shapeId="0" xr:uid="{5333DB67-1CF3-440A-B80F-0E8D01864D65}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A153" authorId="0" shapeId="0" xr:uid="{5312D3E2-95FC-46C4-8084-D33A1D4376D4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A155" authorId="0" shapeId="0" xr:uid="{3CD72E33-0824-4758-9D3B-B4B38A28C9F4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+-2小于
+-1小于等于
+0等于
+1大于等于
+2大于</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A157" authorId="0" shapeId="0" xr:uid="{DF6F44A3-EEBC-4BBB-A2F4-8341B22F5D5E}">
       <text>
         <r>
           <rPr>
@@ -854,7 +974,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="387">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1012,10 +1132,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>600001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>800001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1372,14 +1488,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>判断自己上次使用1022灵归招式是否被破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1022,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>18110221</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2241,6 +2349,162 @@
   </si>
   <si>
     <t>技能首次造成击破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>37000001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReturnFalse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3800004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法使用4键招式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NotUseSomeKeySkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法使用x键招式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3900001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法使用变式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己技能不是武杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600113</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600114</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己技能是武杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己技能不是术杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己技能是术杀式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己技能不是技御式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己技能是技御式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己技能不是法咒式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己技能是法咒式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NotUseVariantSkill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断自己上次使用招式是否被破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判断buff机制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CheckBuffMechanism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,15,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己有猊煞机制buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4001151</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,30391,0,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身至少有1层祖化身30391</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2328,7 +2592,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2346,6 +2610,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2661,7 +2928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F160"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38.125" style="2" customWidth="1"/>
@@ -2737,22 +3004,22 @@
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -2770,1616 +3037,1815 @@
         <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="B12" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="B16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B17" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>260</v>
+        <v>163</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>262</v>
+        <v>166</v>
       </c>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
-        <v>153</v>
+      <c r="B22" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B23" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>157</v>
+      <c r="A23" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>236</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>239</v>
+        <v>175</v>
       </c>
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B28" s="2" t="s">
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="A30" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B31" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>357</v>
+      </c>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B33" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B34" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B35" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B36" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B37" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B38" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B42" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B43" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="D43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B33" s="2" t="s">
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B44" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B45" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B46" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B34" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="D46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B47" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B35" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B36" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D36" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B39" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="F40" s="2"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B41" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F41" s="2"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D42" s="2"/>
-      <c r="F42" s="2"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B43" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43" s="2"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B44" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F44" s="2"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F45" s="2"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B46" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F46" s="2"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B47" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B48" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>79</v>
-      </c>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="F48" s="2"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="F49" s="2"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B50" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>81</v>
+      <c r="A50" s="4" t="s">
+        <v>241</v>
       </c>
       <c r="F50" s="2"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B51" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>239</v>
+      </c>
       <c r="F51" s="2"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B52" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>86</v>
-      </c>
+      <c r="D52" s="2"/>
       <c r="F52" s="2"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>87</v>
+        <v>17</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="F53" s="2"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B54" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="F54" s="2"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F55" s="2"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F56" s="2"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="F57" s="2"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B58" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="F58" s="2"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
-        <v>84</v>
+      <c r="B59" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="F59" s="2"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>83</v>
+        <v>24</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F60" s="2"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="F61" s="2"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B62" s="2" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>94</v>
+        <v>15</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="F62" s="2"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="4" t="s">
-        <v>98</v>
+      <c r="B63" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="F63" s="2"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B64" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="F64" s="2"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B65" s="2" t="s">
-        <v>276</v>
+        <v>47</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>277</v>
+        <v>15</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>278</v>
+        <v>50</v>
       </c>
       <c r="F65" s="2"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="4" t="s">
-        <v>114</v>
+      <c r="B66" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="F66" s="2"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="2" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="F67" s="2"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B68" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="F68" s="2"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="F69" s="2"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B70" s="2" t="s">
-        <v>252</v>
+        <v>81</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="F70" s="2"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B71" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>255</v>
+      <c r="A71" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="F71" s="2"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="4" t="s">
-        <v>127</v>
+      <c r="B72" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="F72" s="2"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B73" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>129</v>
+      <c r="A73" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="F73" s="2"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="4" t="s">
-        <v>134</v>
+      <c r="B74" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="F74" s="2"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B75" s="2" t="s">
-        <v>135</v>
+        <v>273</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>16</v>
+        <v>274</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>346</v>
+        <v>275</v>
       </c>
       <c r="F75" s="2"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B76" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>345</v>
+      <c r="A76" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="F76" s="2"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="4" t="s">
-        <v>146</v>
+      <c r="B77" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="F77" s="2"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A78" s="4" t="s">
-        <v>147</v>
+      <c r="B78" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="F78" s="2"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B79" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>145</v>
+      <c r="A79" s="4" t="s">
+        <v>248</v>
       </c>
       <c r="F79" s="2"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B80" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>248</v>
+        <v>125</v>
       </c>
       <c r="F80" s="2"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B81" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F81" s="2"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B82" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>259</v>
+      <c r="A82" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="F82" s="2"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" s="4" t="s">
-        <v>149</v>
+      <c r="B83" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="F83" s="2"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B84" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>151</v>
+      <c r="A84" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="F84" s="2"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" s="4" t="s">
-        <v>158</v>
+      <c r="B85" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>343</v>
       </c>
       <c r="F85" s="2"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B86" s="2" t="s">
-        <v>161</v>
+        <v>340</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>46</v>
+        <v>341</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>160</v>
+        <v>342</v>
       </c>
       <c r="F86" s="2"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B87" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>163</v>
+      <c r="A87" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="F87" s="2"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="F88" s="2"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B89" s="2" t="s">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="F89" s="2"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A90" s="4" t="s">
-        <v>187</v>
-      </c>
+      <c r="B90" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F90" s="2"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B91" s="2" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>15</v>
+        <v>244</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="F91" s="2"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B92" s="2" t="s">
-        <v>190</v>
+        <v>254</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>189</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="F92" s="2"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>194</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="F93" s="2"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B94" s="2" t="s">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>192</v>
+        <v>145</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>195</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="F94" s="2"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B95" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>211</v>
-      </c>
+      <c r="A95" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F95" s="2"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B96" s="2" t="s">
-        <v>235</v>
+        <v>158</v>
       </c>
       <c r="C96" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F96" s="2"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B97" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F97" s="2"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F98" s="2"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B99" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F99" s="2"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B101" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B102" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B104" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" s="4" t="s">
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B105" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B106" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B108" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B98" s="2" t="s">
+      <c r="D108" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C98" s="2" t="s">
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B110" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A99" s="4" t="s">
+      <c r="D110" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B100" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A101" s="4" t="s">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A111" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B112" s="2" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B102" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D102" s="1" t="s">
+      <c r="C112" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E102" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B103" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A104" s="4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B105" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A106" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B107" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A108" s="4" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B109" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A110" s="4" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B111" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A112" s="4" t="s">
-        <v>279</v>
+      <c r="E112" s="2" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B113" s="2" t="s">
-        <v>280</v>
+        <v>213</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>281</v>
+        <v>210</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>282</v>
+        <v>214</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B114" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>295</v>
+      <c r="A114" s="4" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B115" s="2" t="s">
-        <v>284</v>
+        <v>218</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>281</v>
+        <v>216</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>46</v>
+        <v>217</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>292</v>
+        <v>219</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B116" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>298</v>
+      <c r="A116" s="4" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B117" s="2" t="s">
-        <v>286</v>
+        <v>222</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>281</v>
+        <v>220</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>290</v>
+        <v>221</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>293</v>
+        <v>226</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B118" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>297</v>
+      <c r="A118" s="4" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B119" s="2" t="s">
-        <v>288</v>
+        <v>229</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>281</v>
+        <v>223</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>103</v>
+        <v>228</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>294</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B120" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>296</v>
+      <c r="A120" s="4" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B121" s="2" t="s">
-        <v>328</v>
+        <v>268</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>302</v>
+        <v>16</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B122" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>307</v>
+      <c r="A122" s="4" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B123" s="2" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>304</v>
+        <v>16</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>308</v>
+        <v>279</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B124" s="2" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="C124" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B125" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125" s="4" t="s">
-        <v>310</v>
+      <c r="C125" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B126" s="2" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>327</v>
+        <v>46</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B127" s="2" t="s">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>43</v>
+        <v>287</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>320</v>
+        <v>290</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B128" s="2" t="s">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>46</v>
+        <v>288</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B129" s="2" t="s">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>322</v>
+        <v>291</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B130" s="2" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>290</v>
+        <v>103</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>323</v>
+        <v>293</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B131" s="2" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B132" s="2" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>103</v>
+        <v>300</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B133" s="2" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>104</v>
+        <v>301</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A134" s="4" t="s">
-        <v>329</v>
+      <c r="B134" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B135" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>332</v>
+      <c r="A135" s="4" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B136" s="2" t="s">
-        <v>334</v>
+        <v>308</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>338</v>
+        <v>16</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B137" s="2" t="s">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>337</v>
+        <v>42</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B138" s="2" t="s">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>341</v>
+        <v>45</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A139" s="4" t="s">
-        <v>347</v>
+      <c r="B139" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B140" s="2" t="s">
-        <v>348</v>
+        <v>312</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>349</v>
+        <v>316</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>287</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>350</v>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B141" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B142" s="2" t="s">
-        <v>206</v>
+        <v>314</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>208</v>
+        <v>316</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>207</v>
+        <v>322</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B143" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A144" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B145" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B146" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B147" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B148" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A149" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B150" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A151" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B152" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B154" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A155" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B156" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A157" s="4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B158" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B160" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76552D05-F9DE-49E9-AA4D-34556A3488A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDD9BCE-151B-48D7-9521-CE6D467A9FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4215" yWindow="6120" windowWidth="35565" windowHeight="9315" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -849,97 +849,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A151" authorId="0" shapeId="0" xr:uid="{5333DB67-1CF3-440A-B80F-0E8D01864D65}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
--2小于
--1小于等于
-0等于
-1大于等于
-2大于</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A153" authorId="0" shapeId="0" xr:uid="{5312D3E2-95FC-46C4-8084-D33A1D4376D4}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
--2小于
--1小于等于
-0等于
-1大于等于
-2大于</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A155" authorId="0" shapeId="0" xr:uid="{3CD72E33-0824-4758-9D3B-B4B38A28C9F4}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
--2小于
--1小于等于
-0等于
-1大于等于
-2大于</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A157" authorId="0" shapeId="0" xr:uid="{DF6F44A3-EEBC-4BBB-A2F4-8341B22F5D5E}">
+    <comment ref="A151" authorId="0" shapeId="0" xr:uid="{DF6F44A3-EEBC-4BBB-A2F4-8341B22F5D5E}">
       <text>
         <r>
           <rPr>
@@ -974,7 +884,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="377">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2352,42 +2262,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>37000001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回失败</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReturnFalse</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3800004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无法使用4键招式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NotUseSomeKeySkill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无法使用x键招式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3900001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无法使用变式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>判断自己技能不是武杀式</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2465,10 +2339,6 @@
   </si>
   <si>
     <t>判断自己技能是法咒式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NotUseVariantSkill</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2928,7 +2798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F160"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38.125" style="2" customWidth="1"/>
@@ -3106,16 +2976,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -3343,7 +3213,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
@@ -3352,13 +3222,13 @@
         <v>65</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>25</v>
@@ -3367,13 +3237,13 @@
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
@@ -3382,13 +3252,13 @@
         <v>70</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="F33" s="2"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>25</v>
@@ -3397,67 +3267,67 @@
         <v>67</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="F34" s="2"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="F35" s="2"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="F36" s="2"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="F37" s="2"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="F38" s="2"/>
     </row>
@@ -3983,7 +3853,7 @@
         <v>16</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="F83" s="2"/>
     </row>
@@ -4769,82 +4639,31 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B152" s="2" t="s">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>350</v>
+        <v>370</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>371</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A153" s="4" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B154" s="2" t="s">
-        <v>351</v>
+        <v>203</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>57</v>
+        <v>205</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A155" s="4" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B156" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A157" s="4" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B158" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B160" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E160" s="2" t="s">
         <v>204</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDD9BCE-151B-48D7-9521-CE6D467A9FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F58612-519F-45D7-8061-60253CBC9DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -159,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A73" authorId="0" shapeId="0" xr:uid="{4404A0BB-0684-415F-A1EE-932CF9B368D6}">
+    <comment ref="A70" authorId="0" shapeId="0" xr:uid="{4404A0BB-0684-415F-A1EE-932CF9B368D6}">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A76" authorId="0" shapeId="0" xr:uid="{945C9952-661A-4999-8F70-73F1D7C63160}">
+    <comment ref="A73" authorId="0" shapeId="0" xr:uid="{945C9952-661A-4999-8F70-73F1D7C63160}">
       <text>
         <r>
           <rPr>
@@ -219,7 +219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A79" authorId="0" shapeId="0" xr:uid="{E5FC843F-DA07-43FF-AC47-ED46EFADEA7B}">
+    <comment ref="A76" authorId="0" shapeId="0" xr:uid="{E5FC843F-DA07-43FF-AC47-ED46EFADEA7B}">
       <text>
         <r>
           <rPr>
@@ -249,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A82" authorId="0" shapeId="0" xr:uid="{F4E6CE43-F644-4C3B-ABDC-4422A791C047}">
+    <comment ref="A79" authorId="0" shapeId="0" xr:uid="{F4E6CE43-F644-4C3B-ABDC-4422A791C047}">
       <text>
         <r>
           <rPr>
@@ -279,7 +279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A84" authorId="0" shapeId="0" xr:uid="{C399D82A-C364-479A-A3EC-0765A1AC23FC}">
+    <comment ref="A81" authorId="0" shapeId="0" xr:uid="{C399D82A-C364-479A-A3EC-0765A1AC23FC}">
       <text>
         <r>
           <rPr>
@@ -309,7 +309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A87" authorId="0" shapeId="0" xr:uid="{1F66D5B5-D10B-4952-A6DF-EB0AD1CA976F}">
+    <comment ref="A84" authorId="0" shapeId="0" xr:uid="{1F66D5B5-D10B-4952-A6DF-EB0AD1CA976F}">
       <text>
         <r>
           <rPr>
@@ -339,7 +339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A88" authorId="0" shapeId="0" xr:uid="{85EC1931-B074-4549-93A0-AD9F25FEDB83}">
+    <comment ref="A85" authorId="0" shapeId="0" xr:uid="{85EC1931-B074-4549-93A0-AD9F25FEDB83}">
       <text>
         <r>
           <rPr>
@@ -369,7 +369,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A93" authorId="0" shapeId="0" xr:uid="{6CB726E4-43C1-43F0-9EA8-4B926C41E48E}">
+    <comment ref="A90" authorId="0" shapeId="0" xr:uid="{6CB726E4-43C1-43F0-9EA8-4B926C41E48E}">
       <text>
         <r>
           <rPr>
@@ -399,7 +399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A95" authorId="0" shapeId="0" xr:uid="{48A947BE-D930-4648-AEEF-73C5E3E54577}">
+    <comment ref="A92" authorId="0" shapeId="0" xr:uid="{48A947BE-D930-4648-AEEF-73C5E3E54577}">
       <text>
         <r>
           <rPr>
@@ -429,7 +429,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A98" authorId="0" shapeId="0" xr:uid="{FFA67B4A-F5E9-410C-B978-FA21684F4A99}">
+    <comment ref="A95" authorId="0" shapeId="0" xr:uid="{FFA67B4A-F5E9-410C-B978-FA21684F4A99}">
       <text>
         <r>
           <rPr>
@@ -459,7 +459,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A100" authorId="0" shapeId="0" xr:uid="{C34EDA1F-45FF-465B-8605-9DF11F149AB5}">
+    <comment ref="A97" authorId="0" shapeId="0" xr:uid="{C34EDA1F-45FF-465B-8605-9DF11F149AB5}">
       <text>
         <r>
           <rPr>
@@ -489,7 +489,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A103" authorId="0" shapeId="0" xr:uid="{3C5CD11B-F2CA-45A2-BE89-D1E9F21EB1DF}">
+    <comment ref="A100" authorId="0" shapeId="0" xr:uid="{3C5CD11B-F2CA-45A2-BE89-D1E9F21EB1DF}">
       <text>
         <r>
           <rPr>
@@ -519,7 +519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A107" authorId="0" shapeId="0" xr:uid="{CA1902F7-A507-4529-AA72-0F8B32376739}">
+    <comment ref="A104" authorId="0" shapeId="0" xr:uid="{CA1902F7-A507-4529-AA72-0F8B32376739}">
       <text>
         <r>
           <rPr>
@@ -549,7 +549,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A109" authorId="0" shapeId="0" xr:uid="{218E0718-1A2C-40C8-96DD-53C5CEBF5930}">
+    <comment ref="A106" authorId="0" shapeId="0" xr:uid="{218E0718-1A2C-40C8-96DD-53C5CEBF5930}">
       <text>
         <r>
           <rPr>
@@ -579,7 +579,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A111" authorId="0" shapeId="0" xr:uid="{E8FCF4D6-C27A-404E-9297-2D9C6DC5F649}">
+    <comment ref="A108" authorId="0" shapeId="0" xr:uid="{E8FCF4D6-C27A-404E-9297-2D9C6DC5F649}">
       <text>
         <r>
           <rPr>
@@ -609,7 +609,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A114" authorId="0" shapeId="0" xr:uid="{7B8DA6B6-B8CE-4E4B-A708-BB9B30194380}">
+    <comment ref="A111" authorId="0" shapeId="0" xr:uid="{7B8DA6B6-B8CE-4E4B-A708-BB9B30194380}">
       <text>
         <r>
           <rPr>
@@ -639,7 +639,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A116" authorId="0" shapeId="0" xr:uid="{6C7FF865-48A1-4DF1-8E66-09049149C8DF}">
+    <comment ref="A113" authorId="0" shapeId="0" xr:uid="{6C7FF865-48A1-4DF1-8E66-09049149C8DF}">
       <text>
         <r>
           <rPr>
@@ -669,7 +669,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A118" authorId="0" shapeId="0" xr:uid="{E1905A74-2E51-4936-9C51-A4FAFD9A81F5}">
+    <comment ref="A115" authorId="0" shapeId="0" xr:uid="{E1905A74-2E51-4936-9C51-A4FAFD9A81F5}">
       <text>
         <r>
           <rPr>
@@ -699,7 +699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A120" authorId="0" shapeId="0" xr:uid="{343ABA23-0C71-4DD9-9526-D659AE92536E}">
+    <comment ref="A117" authorId="0" shapeId="0" xr:uid="{343ABA23-0C71-4DD9-9526-D659AE92536E}">
       <text>
         <r>
           <rPr>
@@ -729,7 +729,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A122" authorId="0" shapeId="0" xr:uid="{91D3FFAD-AAB8-4AE8-A0E7-42FFED952D55}">
+    <comment ref="A119" authorId="0" shapeId="0" xr:uid="{91D3FFAD-AAB8-4AE8-A0E7-42FFED952D55}">
       <text>
         <r>
           <rPr>
@@ -759,7 +759,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A135" authorId="0" shapeId="0" xr:uid="{0C9DF881-3498-4E87-9087-181B115A5E71}">
+    <comment ref="A132" authorId="0" shapeId="0" xr:uid="{0C9DF881-3498-4E87-9087-181B115A5E71}">
       <text>
         <r>
           <rPr>
@@ -789,7 +789,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A144" authorId="0" shapeId="0" xr:uid="{63285060-972C-4852-9EDD-206CF2B2818F}">
+    <comment ref="A141" authorId="0" shapeId="0" xr:uid="{63285060-972C-4852-9EDD-206CF2B2818F}">
       <text>
         <r>
           <rPr>
@@ -819,7 +819,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A149" authorId="0" shapeId="0" xr:uid="{649C4F38-1020-4339-86B1-D2195E611C1D}">
+    <comment ref="A146" authorId="0" shapeId="0" xr:uid="{649C4F38-1020-4339-86B1-D2195E611C1D}">
       <text>
         <r>
           <rPr>
@@ -849,7 +849,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A151" authorId="0" shapeId="0" xr:uid="{DF6F44A3-EEBC-4BBB-A2F4-8341B22F5D5E}">
+    <comment ref="A148" authorId="0" shapeId="0" xr:uid="{DF6F44A3-EEBC-4BBB-A2F4-8341B22F5D5E}">
       <text>
         <r>
           <rPr>
@@ -884,7 +884,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="372">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1018,10 +1018,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CheckBeDamageHpReduce</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>100001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1050,10 +1046,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1100001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1219,18 +1211,6 @@
   </si>
   <si>
     <t>判断是否互为目标</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1100002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>判断自己是否被破盾打到生命了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>判断对方是否被破盾打到生命了</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2798,7 +2778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F154"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38.125" style="2" customWidth="1"/>
@@ -2865,7 +2845,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
@@ -2874,22 +2854,22 @@
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -2901,91 +2881,91 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -2997,46 +2977,46 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F16" s="2"/>
     </row>
@@ -3048,142 +3028,142 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -3192,7 +3172,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>21</v>
@@ -3213,22 +3193,22 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>25</v>
@@ -3237,97 +3217,97 @@
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="F33" s="2"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F34" s="2"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="F35" s="2"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="F36" s="2"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F37" s="2"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F38" s="2"/>
     </row>
@@ -3342,7 +3322,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>26</v>
@@ -3351,82 +3331,82 @@
         <v>16</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F42" s="2"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F43" s="2"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F44" s="2"/>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F45" s="2"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F46" s="2"/>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -3435,7 +3415,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>27</v>
@@ -3450,22 +3430,22 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F50" s="2"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -3475,7 +3455,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>24</v>
@@ -3484,112 +3464,112 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F53" s="2"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F54" s="2"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F55" s="2"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F56" s="2"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F57" s="2"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B58" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F58" s="2"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F59" s="2"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -3598,681 +3578,690 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B62" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>85</v>
+      <c r="E62" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="F62" s="2"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>86</v>
+        <v>46</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="F63" s="2"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B64" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="F64" s="2"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B65" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C65" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E65" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F65" s="2"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B66" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>51</v>
+      <c r="A66" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="F66" s="2"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="2" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="F67" s="2"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B68" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>58</v>
+      <c r="A68" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="F68" s="2"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="4" t="s">
-        <v>83</v>
+      <c r="B69" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="F69" s="2"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B70" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>83</v>
+      <c r="A70" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="F70" s="2"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="4" t="s">
-        <v>92</v>
+      <c r="B71" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="F71" s="2"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B72" s="2" t="s">
-        <v>90</v>
+        <v>268</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>94</v>
+        <v>269</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>93</v>
+        <v>270</v>
       </c>
       <c r="F72" s="2"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="F73" s="2"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B74" s="2" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F74" s="2"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B75" s="2" t="s">
-        <v>273</v>
+        <v>106</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>274</v>
+        <v>15</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>275</v>
+        <v>109</v>
       </c>
       <c r="F75" s="2"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>113</v>
+        <v>243</v>
       </c>
       <c r="F76" s="2"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B77" s="2" t="s">
-        <v>117</v>
+        <v>244</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>116</v>
+        <v>242</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F77" s="2"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B78" s="2" t="s">
-        <v>111</v>
+        <v>246</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>15</v>
+        <v>245</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>114</v>
+        <v>247</v>
       </c>
       <c r="F78" s="2"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>248</v>
+        <v>121</v>
       </c>
       <c r="F79" s="2"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B80" s="2" t="s">
-        <v>249</v>
+        <v>123</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>247</v>
+        <v>16</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>125</v>
+        <v>363</v>
       </c>
       <c r="F80" s="2"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B81" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>252</v>
+      <c r="A81" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="F81" s="2"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" s="4" t="s">
-        <v>126</v>
+      <c r="B82" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="F82" s="2"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B83" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="D83" s="1" t="s">
-        <v>16</v>
+        <v>336</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>368</v>
+        <v>337</v>
       </c>
       <c r="F83" s="2"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F84" s="2"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B85" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>343</v>
+      <c r="A85" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="F85" s="2"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B86" s="2" t="s">
-        <v>340</v>
+        <v>134</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>341</v>
+        <v>136</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>342</v>
+        <v>137</v>
       </c>
       <c r="F86" s="2"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" s="4" t="s">
-        <v>143</v>
+      <c r="B87" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>240</v>
       </c>
       <c r="F87" s="2"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A88" s="4" t="s">
-        <v>144</v>
+      <c r="B88" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="F88" s="2"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B89" s="2" t="s">
-        <v>139</v>
+        <v>249</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D89" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F89" s="2"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F89" s="2"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B90" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="F90" s="2"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B91" s="2" t="s">
-        <v>253</v>
+        <v>144</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>140</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>244</v>
+        <v>142</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>243</v>
+        <v>143</v>
       </c>
       <c r="F91" s="2"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B92" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>256</v>
+      <c r="A92" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="F92" s="2"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A93" s="4" t="s">
-        <v>146</v>
+      <c r="B93" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="F93" s="2"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B94" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F94" s="2"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="F95" s="2"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B96" s="2" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="F96" s="2"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B97" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F97" s="2"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98" s="4" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B98" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F98" s="2"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C98" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B99" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>178</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>177</v>
+        <v>15</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F99" s="2"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B101" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B101" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="D101" s="1" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B102" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>15</v>
+        <v>202</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A103" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B103" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B105" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B104" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B105" s="2" t="s">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B107" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B109" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E105" s="2" t="s">
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B110" s="2" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B106" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A107" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B108" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A109" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B110" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="C110" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B112" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D112" s="1" t="s">
+      <c r="E112" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B114" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B116" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B118" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E112" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B113" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B115" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A116" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B117" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A118" s="4" t="s">
-        <v>224</v>
+      <c r="E118" s="2" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B119" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>227</v>
+      <c r="A119" s="4" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A120" s="4" t="s">
-        <v>267</v>
+      <c r="B120" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B121" s="2" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122" s="4" t="s">
+      <c r="B122" s="2" t="s">
         <v>276</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
@@ -4280,38 +4269,38 @@
         <v>277</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B124" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>42</v>
+        <v>282</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B125" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>45</v>
+        <v>283</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>289</v>
@@ -4319,352 +4308,310 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B126" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B127" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B128" s="2" t="s">
-        <v>284</v>
+        <v>320</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B129" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>102</v>
+        <v>295</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B130" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>103</v>
+        <v>296</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B131" s="2" t="s">
-        <v>325</v>
+        <v>293</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B132" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>304</v>
+      <c r="A132" s="4" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B133" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>305</v>
+        <v>16</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B134" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>302</v>
+        <v>40</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A135" s="4" t="s">
-        <v>307</v>
+      <c r="B135" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B136" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E136" s="5" t="s">
-        <v>324</v>
+        <v>44</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B137" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>42</v>
+        <v>282</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B138" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C138" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E138" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B139" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C139" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C139" s="2" t="s">
-        <v>316</v>
-      </c>
       <c r="D139" s="1" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B140" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B141" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E141" s="2" t="s">
+      <c r="A141" s="4" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B142" s="2" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>102</v>
+        <v>323</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B143" s="2" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>103</v>
+        <v>328</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A144" s="4" t="s">
-        <v>326</v>
+      <c r="B144" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B145" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B146" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>335</v>
+      <c r="A146" s="4" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B147" s="2" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B148" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>339</v>
+      <c r="A148" s="4" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A149" s="4" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B150" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>347</v>
+      <c r="B149" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A151" s="4" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B152" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B154" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>204</v>
+      <c r="B151" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F58612-519F-45D7-8061-60253CBC9DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EF451B-3090-4444-9B82-E7DF89167976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
+++ b/Luban/Config/Datas/#BattleMomentConditionConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EF451B-3090-4444-9B82-E7DF89167976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361D2EC4-E9FC-4B57-B988-E225EA02620E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
